--- a/data/P1/P1T3_BQ8.xlsx
+++ b/data/P1/P1T3_BQ8.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A227D2-701D-E643-A114-D6696434187F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533D58C2-09AC-384E-A655-BDEF35030D81}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38220" yWindow="6080" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="38220" yWindow="6080" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="74">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -162,13 +162,106 @@
   </si>
   <si>
     <t>可愛的、美妙的</t>
+  </si>
+  <si>
+    <t>phonetics</t>
+  </si>
+  <si>
+    <t>syllable</t>
+  </si>
+  <si>
+    <t>/ˈɪnstrəmənts/</t>
+  </si>
+  <si>
+    <t>in-stru-ments</t>
+  </si>
+  <si>
+    <t>/ˈsɪmblz/</t>
+  </si>
+  <si>
+    <t>cym-bals</t>
+  </si>
+  <si>
+    <t>/ˌtæmbəˈriːn/</t>
+  </si>
+  <si>
+    <t>tam-bou-rine</t>
+  </si>
+  <si>
+    <t>/ˈzaɪləfəʊn/</t>
+  </si>
+  <si>
+    <t>xy-lo-phone</t>
+  </si>
+  <si>
+    <t>/drʌm/</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>/ˈtraɪæŋkl/</t>
+  </si>
+  <si>
+    <t>tri-an-gle</t>
+  </si>
+  <si>
+    <t>/ʃeɪk/</t>
+  </si>
+  <si>
+    <t>/straɪk/</t>
+  </si>
+  <si>
+    <t>/piˈænəʊ/</t>
+  </si>
+  <si>
+    <t>pi-a-no</t>
+  </si>
+  <si>
+    <t>/ɡɪˈtɑː(r)/</t>
+  </si>
+  <si>
+    <t>gui-tar</t>
+  </si>
+  <si>
+    <t>/ˌvaɪəˈlɪn/</t>
+  </si>
+  <si>
+    <t>vi-o-lin</t>
+  </si>
+  <si>
+    <t>/fluːt/</t>
+  </si>
+  <si>
+    <t>/fɑːst/</t>
+  </si>
+  <si>
+    <t>/sləʊ/</t>
+  </si>
+  <si>
+    <t>/laʊd/</t>
+  </si>
+  <si>
+    <t>/sɒft/</t>
+  </si>
+  <si>
+    <t>/ˈɔːfl/</t>
+  </si>
+  <si>
+    <t>aw-ful</t>
+  </si>
+  <si>
+    <t>/ˈlʌvli/</t>
+  </si>
+  <si>
+    <t>love-ly</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -211,6 +304,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -220,12 +321,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -234,7 +350,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -248,6 +364,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -564,14 +683,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -581,11 +703,19 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3"/>
+      <c r="D1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -595,9 +725,14 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="D2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -607,8 +742,14 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -618,8 +759,14 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -629,8 +776,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -640,8 +793,14 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -651,8 +810,14 @@
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -662,8 +827,14 @@
       <c r="C8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="D8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -673,8 +844,14 @@
       <c r="C9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -684,8 +861,14 @@
       <c r="C10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -695,8 +878,14 @@
       <c r="C11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,8 +895,14 @@
       <c r="C12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="D12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -717,8 +912,14 @@
       <c r="C13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -728,8 +929,14 @@
       <c r="C14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="D14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -739,8 +946,14 @@
       <c r="C15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -750,8 +963,14 @@
       <c r="C16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -761,8 +980,14 @@
       <c r="C17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -772,8 +997,14 @@
       <c r="C18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -783,26 +1014,32 @@
       <c r="C19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:5">
       <c r="A21" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:5">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:5">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:5">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>

--- a/data/P1/P1T3_BQ8.xlsx
+++ b/data/P1/P1T3_BQ8.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/English/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533D58C2-09AC-384E-A655-BDEF35030D81}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3A87E7-335F-9A4C-B7C6-BBBB1035B26F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38220" yWindow="6080" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -255,6 +255,64 @@
   </si>
   <si>
     <t>love-ly</t>
+  </si>
+  <si>
+    <t>English explanation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tools we use to make music</t>
+  </si>
+  <si>
+    <t>Two round metal plates; hit them for loud sound</t>
+  </si>
+  <si>
+    <t>Round drum with small metal jingles, you shake or hit it</t>
+  </si>
+  <si>
+    <t>Colorful bars; hit bars to make high and low music</t>
+  </si>
+  <si>
+    <t>Round music tool, hit it with sticks to make beats</t>
+  </si>
+  <si>
+    <t>Small metal three-sided tool; tap it for clear sound</t>
+  </si>
+  <si>
+    <t>Move a music tool back and forth to make sound</t>
+  </si>
+  <si>
+    <t>Hit an instrument to make music</t>
+  </si>
+  <si>
+    <t>Big keyboard instrument, press keys to play songs</t>
+  </si>
+  <si>
+    <t>String instrument; pull strings with your fingers</t>
+  </si>
+  <si>
+    <t>Small string instrument, play it with a thin stick</t>
+  </si>
+  <si>
+    <t>Long thin wind instrument; blow air to make sound</t>
+  </si>
+  <si>
+    <t>Music with quick beats</t>
+  </si>
+  <si>
+    <t>Music with gentle, slow beats</t>
+  </si>
+  <si>
+    <t>Very big, strong sound</t>
+  </si>
+  <si>
+    <t>Quiet, gentle sound</t>
+  </si>
+  <si>
+    <t>Sounds not nice to listen to</t>
+  </si>
+  <si>
+    <t>Sounds beautiful and nice</t>
   </si>
 </sst>
 </file>
@@ -709,7 +767,9 @@
       <c r="E1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -731,6 +791,9 @@
       <c r="E2" t="s">
         <v>46</v>
       </c>
+      <c r="F2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
@@ -748,6 +811,9 @@
       <c r="E3" t="s">
         <v>48</v>
       </c>
+      <c r="F3" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
@@ -765,6 +831,9 @@
       <c r="E4" t="s">
         <v>50</v>
       </c>
+      <c r="F4" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
@@ -782,6 +851,9 @@
       <c r="E5" t="s">
         <v>52</v>
       </c>
+      <c r="F5" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
@@ -799,6 +871,9 @@
       <c r="E6" t="s">
         <v>54</v>
       </c>
+      <c r="F6" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
@@ -816,6 +891,9 @@
       <c r="E7" t="s">
         <v>56</v>
       </c>
+      <c r="F7" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
@@ -833,6 +911,9 @@
       <c r="E8" t="s">
         <v>54</v>
       </c>
+      <c r="F8" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
@@ -850,6 +931,9 @@
       <c r="E9" t="s">
         <v>54</v>
       </c>
+      <c r="F9" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
@@ -867,6 +951,9 @@
       <c r="E10" t="s">
         <v>60</v>
       </c>
+      <c r="F10" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
@@ -884,6 +971,9 @@
       <c r="E11" t="s">
         <v>62</v>
       </c>
+      <c r="F11" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
@@ -901,6 +991,9 @@
       <c r="E12" t="s">
         <v>64</v>
       </c>
+      <c r="F12" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
@@ -918,6 +1011,9 @@
       <c r="E13" t="s">
         <v>54</v>
       </c>
+      <c r="F13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
@@ -935,6 +1031,9 @@
       <c r="E14" t="s">
         <v>54</v>
       </c>
+      <c r="F14" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
@@ -952,6 +1051,9 @@
       <c r="E15" t="s">
         <v>54</v>
       </c>
+      <c r="F15" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
@@ -969,8 +1071,11 @@
       <c r="E16" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -986,8 +1091,11 @@
       <c r="E17" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -1003,8 +1111,11 @@
       <c r="E18" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -1020,26 +1131,29 @@
       <c r="E19" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:6">
       <c r="A21" s="2"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:6">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>
